--- a/MetaData.xlsx
+++ b/MetaData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinzh\Dropbox\On_Going_Things\MultiScale_Project\PFM_Repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6E54AE3-D305-402D-AC9B-A7CB2BF1C79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC964B64-6699-4B4C-BFEF-F8888E6A6FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="4" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="85">
   <si>
     <t>PTt path. Put control points here. Interpolatation will be done automatically</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -132,10 +132,6 @@
   </si>
   <si>
     <t>{100}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{101}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -725,7 +721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{189715F9-88C1-473E-8CE8-6457A6A764DF}">
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29" style="2" customWidth="1"/>
@@ -733,14 +729,14 @@
     <col min="3" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>14</v>
@@ -748,125 +744,116 @@
       <c r="C2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="4" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="B4" s="3">
         <v>2.0000000000000002E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B7" s="3">
         <v>1000000000</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B8" s="3">
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B9" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B10" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
+      <c r="B14" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="3">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
+      <c r="B15" s="3">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="B16" s="3">
-        <v>1.0000000000000001E-15</v>
+        <v>9.9999999999999998E-13</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="2">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="2">
         <v>100</v>
@@ -874,7 +861,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" s="2">
         <v>0</v>
@@ -882,7 +869,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B21" s="2">
         <v>8</v>
@@ -890,7 +877,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B22" s="2">
         <v>1.1499999999999999</v>
@@ -898,7 +885,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B23" s="2">
         <v>0.5</v>
@@ -906,7 +893,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B24" s="2">
         <v>0.25</v>
@@ -914,7 +901,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B25" s="3">
         <v>1E-8</v>
@@ -922,7 +909,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B26" s="2">
         <v>3</v>
@@ -930,7 +917,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B27" s="2">
         <v>1</v>
@@ -938,7 +925,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B28" s="2">
         <v>0</v>
@@ -946,7 +933,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B29" s="2">
         <v>1</v>
@@ -954,7 +941,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B30" s="2">
         <v>0.1</v>
@@ -962,7 +949,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B31" s="2">
         <v>0</v>
@@ -970,7 +957,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B32" s="3">
         <v>1E-8</v>
@@ -978,7 +965,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B33" s="2">
         <v>16</v>
@@ -986,15 +973,15 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B35" s="3">
         <v>1E-8</v>
@@ -1002,7 +989,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B36" s="2">
         <v>500</v>
@@ -1010,7 +997,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B37" s="2">
         <v>1</v>
@@ -1018,7 +1005,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B38" s="2">
         <v>5</v>
@@ -1026,7 +1013,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B39" s="2">
         <v>1</v>
@@ -1034,7 +1021,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B40" s="2">
         <v>1</v>
@@ -1042,7 +1029,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B41" s="2">
         <v>1</v>
@@ -1050,7 +1037,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B42" s="2">
         <v>10</v>
@@ -1058,7 +1045,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B43" s="2">
         <v>10</v>
@@ -1066,7 +1053,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B44" s="2">
         <v>0</v>
@@ -1074,12 +1061,12 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B47" s="2">
         <v>1</v>
@@ -1087,7 +1074,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B48" s="3">
         <v>1.0000000000000001E-9</v>
@@ -1095,7 +1082,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B49" s="3">
         <v>0.01</v>
@@ -1103,7 +1090,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B50" s="2">
         <v>1</v>
@@ -1111,7 +1098,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B51" s="2">
         <v>0.5</v>
@@ -1119,10 +1106,10 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +1149,7 @@
         <v>1000000000</v>
       </c>
       <c r="B4">
-        <v>1800</v>
+        <v>2135</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1173,7 +1160,7 @@
         <v>1000000000</v>
       </c>
       <c r="B5">
-        <v>1800</v>
+        <v>2135</v>
       </c>
       <c r="C5" s="1">
         <v>10000000000</v>
@@ -1188,6 +1175,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1254,7 +1242,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>14</v>
@@ -1377,10 +1365,10 @@
         <v>20</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1391,7 +1379,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AD31C97-603F-4CE3-9593-050F54A5E117}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.25" style="2" customWidth="1"/>
@@ -1439,35 +1427,35 @@
       <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="B6" s="2">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>12</v>
       </c>
+      <c r="B7" s="2">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
+      <c r="B8" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -1480,15 +1468,6 @@
       <c r="C11" s="2">
         <v>0</v>
       </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
@@ -1500,85 +1479,25 @@
       <c r="C12" s="3">
         <v>9.9999999999999998E-13</v>
       </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="2">
-        <v>0</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3">
-        <v>9.9999999999999998E-13</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
+      <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="2">
-        <v>0</v>
-      </c>
-      <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>9.9999999999999998E-13</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
+      <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="2">
-        <v>0</v>
-      </c>
-      <c r="C15" s="2">
-        <v>0</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>9.9999999999999998E-13</v>
-      </c>
+      <c r="F15" s="3"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -1589,29 +1508,18 @@
         <v>0</v>
       </c>
       <c r="C18" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B19" s="2">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="C19" s="2">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="2">
-        <v>90</v>
-      </c>
-      <c r="C20" s="2">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1634,7 +1542,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -1683,7 +1591,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>14</v>
@@ -1806,10 +1714,10 @@
         <v>20</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1832,7 +1740,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -1881,7 +1789,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>14</v>
@@ -2004,10 +1912,10 @@
         <v>20</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2030,7 +1938,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -2079,7 +1987,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>14</v>
@@ -2202,10 +2110,10 @@
         <v>20</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2228,7 +2136,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -2277,7 +2185,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>14</v>
@@ -2400,10 +2308,10 @@
         <v>20</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2426,7 +2334,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -2475,22 +2383,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -2503,15 +2402,6 @@
       <c r="C11" s="2">
         <v>0</v>
       </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
-      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
@@ -2523,85 +2413,25 @@
       <c r="C12" s="3">
         <v>9.9999999999999998E-13</v>
       </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="2">
-        <v>0</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3">
-        <v>9.9999999999999998E-13</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
+      <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="2">
-        <v>0</v>
-      </c>
-      <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>9.9999999999999998E-13</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
+      <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="2">
-        <v>0</v>
-      </c>
-      <c r="C15" s="2">
-        <v>0</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>9.9999999999999998E-13</v>
-      </c>
+      <c r="F15" s="3"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/MetaData.xlsx
+++ b/MetaData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinzh\Dropbox\On_Going_Things\MultiScale_Project\PFM_Repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC964B64-6699-4B4C-BFEF-F8888E6A6FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4711AE2-EC53-4D59-A75D-5A654E68F7B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="4" r:id="rId1"/>
@@ -795,7 +795,7 @@
         <v>32</v>
       </c>
       <c r="B10" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -816,7 +816,7 @@
         <v>34</v>
       </c>
       <c r="B14" s="3">
-        <v>50</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1146,10 +1146,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>1000000000</v>
+        <v>1500000000</v>
       </c>
       <c r="B4">
-        <v>2135</v>
+        <v>2162</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1157,10 +1157,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>1000000000</v>
+        <v>1500000000</v>
       </c>
       <c r="B5">
-        <v>2135</v>
+        <v>2162</v>
       </c>
       <c r="C5" s="1">
         <v>10000000000</v>
@@ -1428,7 +1428,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="2">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -1436,7 +1436,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="2">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -1444,7 +1444,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="2">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -1463,7 +1463,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="3">
-        <v>9.9999999999999998E-13</v>
+        <v>1E-25</v>
       </c>
       <c r="C11" s="2">
         <v>0</v>
@@ -1477,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3">
-        <v>9.9999999999999998E-13</v>
+        <v>1E-25</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -2397,7 +2397,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="3">
-        <v>9.9999999999999998E-13</v>
+        <v>1E-25</v>
       </c>
       <c r="C11" s="2">
         <v>0</v>
@@ -2411,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3">
-        <v>9.9999999999999998E-13</v>
+        <v>1E-25</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">

--- a/MetaData.xlsx
+++ b/MetaData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinzh\Dropbox\On_Going_Things\MultiScale_Project\PFM_Repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4711AE2-EC53-4D59-A75D-5A654E68F7B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F141C9-7EAC-45F1-A7B1-18C3E3DADCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="4" r:id="rId1"/>
@@ -816,7 +816,7 @@
         <v>34</v>
       </c>
       <c r="B14" s="3">
-        <v>1000</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -1428,7 +1428,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="2">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -1436,7 +1436,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="2">
-        <v>0.01</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -1444,7 +1444,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="2">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">

--- a/MetaData.xlsx
+++ b/MetaData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinzh\Dropbox\On_Going_Things\MultiScale_Project\PFM_Repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F141C9-7EAC-45F1-A7B1-18C3E3DADCE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA74C404-F70F-497E-836E-F199DB7990CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="4" r:id="rId1"/>
@@ -20,8 +20,10 @@
     <sheet name="Quartz" sheetId="6" r:id="rId5"/>
     <sheet name="Kyanite" sheetId="7" r:id="rId6"/>
     <sheet name="Clinopyroxene" sheetId="8" r:id="rId7"/>
-    <sheet name="Feldspar" sheetId="9" r:id="rId8"/>
-    <sheet name="Melt" sheetId="5" r:id="rId9"/>
+    <sheet name="Orthopyroxene" sheetId="11" r:id="rId8"/>
+    <sheet name="Feldspar" sheetId="9" r:id="rId9"/>
+    <sheet name="Melt" sheetId="5" r:id="rId10"/>
+    <sheet name="Melt(H18)" sheetId="10" r:id="rId11"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="86">
   <si>
     <t>PTt path. Put control points here. Interpolatation will be done automatically</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -123,18 +125,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>facet</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{001}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{100}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Theta</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -362,15 +352,29 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Feldspar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Update PT every</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Interface damp W factor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Kyanite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Clinopyroxene</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Feldspar</t>
+  </si>
+  <si>
+    <t>Melt(H18)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Orthopyroxene</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -378,7 +382,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -397,6 +401,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -438,8 +451,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -721,22 +734,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{189715F9-88C1-473E-8CE8-6457A6A764DF}">
-  <dimension ref="A1:C52"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29" style="2" customWidth="1"/>
     <col min="2" max="2" width="11.625" style="2" customWidth="1"/>
     <col min="3" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>14</v>
@@ -744,92 +757,98 @@
       <c r="C2" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B4" s="3">
         <v>2.0000000000000002E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B7" s="3">
         <v>1000000000</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B8" s="3">
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B9" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+      <c r="B15" s="3">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="B11" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="3">
-        <v>10000000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="B16" s="3">
         <v>9.9999999999999998E-13</v>
@@ -837,23 +856,23 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B17" s="2">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B18" s="2">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B19" s="2">
         <v>100</v>
@@ -861,7 +880,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B20" s="2">
         <v>0</v>
@@ -869,7 +888,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B21" s="2">
         <v>8</v>
@@ -877,7 +896,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B22" s="2">
         <v>1.1499999999999999</v>
@@ -885,7 +904,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B23" s="2">
         <v>0.5</v>
@@ -893,7 +912,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B24" s="2">
         <v>0.25</v>
@@ -901,7 +920,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B25" s="3">
         <v>1E-8</v>
@@ -909,7 +928,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B26" s="2">
         <v>3</v>
@@ -917,7 +936,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B27" s="2">
         <v>1</v>
@@ -925,7 +944,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B28" s="2">
         <v>0</v>
@@ -933,23 +952,23 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B29" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
-        <v>50</v>
+      <c r="A30" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="B30" s="2">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B31" s="2">
         <v>0</v>
@@ -957,7 +976,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B32" s="3">
         <v>1E-8</v>
@@ -965,7 +984,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B33" s="2">
         <v>16</v>
@@ -973,23 +992,23 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B35" s="3">
-        <v>1E-8</v>
+        <v>1E-10</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B36" s="2">
         <v>500</v>
@@ -997,7 +1016,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B37" s="2">
         <v>1</v>
@@ -1005,15 +1024,15 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B38" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B39" s="2">
         <v>1</v>
@@ -1021,7 +1040,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B40" s="2">
         <v>1</v>
@@ -1029,7 +1048,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B41" s="2">
         <v>1</v>
@@ -1037,36 +1056,36 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B42" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B43" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B44" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" s="5" t="s">
-        <v>66</v>
+      <c r="A46" s="6" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B47" s="2">
         <v>1</v>
@@ -1074,7 +1093,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B48" s="3">
         <v>1.0000000000000001E-9</v>
@@ -1082,7 +1101,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B49" s="3">
         <v>0.01</v>
@@ -1090,26 +1109,450 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B50" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51" s="2" t="s">
-        <v>73</v>
+      <c r="A51" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="B51" s="2">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B53" s="2">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025FDC18-195D-4905-B685-5FA04D5B62BC}">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1E-25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41D8EF3E-EA7F-4736-966B-1CF8D5A8AF27}">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1E-25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1146,10 +1589,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>1500000000</v>
+        <v>300000000</v>
       </c>
       <c r="B4">
-        <v>2162</v>
+        <v>400</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1157,20 +1600,36 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>1500000000</v>
+        <v>300000000</v>
       </c>
       <c r="B5">
-        <v>2162</v>
+        <v>400</v>
       </c>
       <c r="C5" s="1">
-        <v>10000000000</v>
+        <v>500000000</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C6" s="1"/>
+      <c r="A6" s="1">
+        <v>1000000000</v>
+      </c>
+      <c r="B6">
+        <v>973</v>
+      </c>
+      <c r="C6" s="1">
+        <v>5000000000</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C7" s="1"/>
+      <c r="A7" s="1">
+        <v>1000000000</v>
+      </c>
+      <c r="B7">
+        <v>973</v>
+      </c>
+      <c r="C7" s="1">
+        <v>10000000000000</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1181,10 +1640,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E05623AC-7B59-47E4-814D-E3135FA16D14}">
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.25" style="2" customWidth="1"/>
+    <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
     <col min="2" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1203,92 +1662,82 @@
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="D2" s="5"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="B3" s="2">
-        <v>0.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" s="2" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="3">
-        <v>1E-14</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="2">
-        <v>0</v>
-      </c>
-      <c r="C12" s="3">
-        <v>1E-14</v>
+        <v>14</v>
+      </c>
+      <c r="B12" s="3">
+        <v>9.9999999999999997E-29</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -1302,16 +1751,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="2">
         <v>0</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3">
-        <v>1E-14</v>
+      <c r="C13" s="3">
+        <v>9.9999999999999997E-29</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
@@ -1322,7 +1771,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2">
         <v>0</v>
@@ -1330,11 +1779,11 @@
       <c r="C14" s="2">
         <v>0</v>
       </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>1E-14</v>
+      <c r="D14" s="3">
+        <v>9.9999999999999997E-29</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -1342,33 +1791,56 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>9.9999999999999997E-29</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="2">
-        <v>0</v>
-      </c>
-      <c r="C15" s="2">
-        <v>0</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1E-14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>9.9999999999999997E-29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>26</v>
+      <c r="B18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1379,10 +1851,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AD31C97-603F-4CE3-9593-050F54A5E117}">
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.25" style="2" customWidth="1"/>
+    <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
     <col min="2" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1401,125 +1873,182 @@
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="D2" s="5"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="B3" s="2">
-        <v>0.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0.4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2">
-        <v>0.2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" s="2" t="s">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="3">
-        <v>1E-25</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0</v>
+      <c r="D11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="2">
-        <v>0</v>
-      </c>
-      <c r="C12" s="3">
-        <v>1E-25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D13" s="3"/>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="E14" s="3"/>
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F15" s="3"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1E-25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="2">
-        <v>0</v>
-      </c>
-      <c r="C18" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="2" t="s">
+      <c r="B18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="B19" s="2">
-        <v>90</v>
-      </c>
-      <c r="C19" s="2">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1530,10 +2059,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FF107C2-8A37-4D64-A550-09EEF500952A}">
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.25" style="2" customWidth="1"/>
+    <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
     <col min="2" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1542,7 +2071,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -1552,92 +2081,82 @@
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="D2" s="5"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="B3" s="2">
-        <v>0.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" s="2" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="3">
-        <v>9.9999999999999998E-13</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="2">
-        <v>0</v>
-      </c>
-      <c r="C12" s="3">
-        <v>9.9999999999999998E-13</v>
+        <v>14</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -1651,16 +2170,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="2">
         <v>0</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3">
-        <v>9.9999999999999998E-13</v>
+      <c r="C13" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
@@ -1671,7 +2190,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2">
         <v>0</v>
@@ -1679,11 +2198,11 @@
       <c r="C14" s="2">
         <v>0</v>
       </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>9.9999999999999998E-13</v>
+      <c r="D14" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -1691,33 +2210,53 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="2">
-        <v>0</v>
-      </c>
-      <c r="C15" s="2">
-        <v>0</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>9.9999999999999998E-13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1E-25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>26</v>
+      <c r="B18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1728,10 +2267,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63151BAD-3F80-45D4-892B-9A6DD90D0F1A}">
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.25" style="2" customWidth="1"/>
+    <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
     <col min="2" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1750,92 +2289,82 @@
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="D2" s="5"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="B3" s="2">
-        <v>0.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" s="2" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="3">
-        <v>9.9999999999999998E-13</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="2">
-        <v>0</v>
-      </c>
-      <c r="C12" s="3">
-        <v>9.9999999999999998E-13</v>
+        <v>14</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -1849,16 +2378,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="2">
         <v>0</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3">
-        <v>9.9999999999999998E-13</v>
+      <c r="C13" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
@@ -1869,7 +2398,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2">
         <v>0</v>
@@ -1877,11 +2406,11 @@
       <c r="C14" s="2">
         <v>0</v>
       </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>9.9999999999999998E-13</v>
+      <c r="D14" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -1889,33 +2418,53 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="2">
-        <v>0</v>
-      </c>
-      <c r="C15" s="2">
-        <v>0</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>9.9999999999999998E-13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1E-25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>26</v>
+      <c r="B18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1926,10 +2475,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1655C2AE-3514-4AA5-8179-DD282EB7D835}">
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.25" style="2" customWidth="1"/>
+    <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
     <col min="2" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1937,7 +2486,7 @@
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1948,92 +2497,82 @@
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="D2" s="5"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="B3" s="2">
-        <v>0.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" s="2" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="3">
-        <v>9.9999999999999998E-13</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="2">
-        <v>0</v>
-      </c>
-      <c r="C12" s="3">
-        <v>9.9999999999999998E-13</v>
+        <v>14</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -2047,16 +2586,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="2">
         <v>0</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3">
-        <v>9.9999999999999998E-13</v>
+      <c r="C13" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
@@ -2067,7 +2606,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2">
         <v>0</v>
@@ -2075,11 +2614,11 @@
       <c r="C14" s="2">
         <v>0</v>
       </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>9.9999999999999998E-13</v>
+      <c r="D14" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -2087,33 +2626,53 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="2">
-        <v>0</v>
-      </c>
-      <c r="C15" s="2">
-        <v>0</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>9.9999999999999998E-13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1E-25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>26</v>
+      <c r="B18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2123,11 +2682,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12423AB5-F589-4113-94B0-34077D332A14}">
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6592A610-98F2-4892-B0FE-DFC4003883EF}">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.25" style="2" customWidth="1"/>
+    <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
     <col min="2" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -2135,8 +2694,8 @@
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>84</v>
+      <c r="B1" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -2146,92 +2705,82 @@
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="D2" s="5"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="B3" s="2">
-        <v>0.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" s="2" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="3">
-        <v>9.9999999999999998E-13</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2">
-        <v>0</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="2">
-        <v>0</v>
-      </c>
-      <c r="C12" s="3">
-        <v>9.9999999999999998E-13</v>
+        <v>14</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -2245,16 +2794,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13" s="2">
         <v>0</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="3">
-        <v>9.9999999999999998E-13</v>
+      <c r="C13" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
@@ -2265,7 +2814,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2">
         <v>0</v>
@@ -2273,11 +2822,11 @@
       <c r="C14" s="2">
         <v>0</v>
       </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>9.9999999999999998E-13</v>
+      <c r="D14" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -2285,33 +2834,53 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="2">
-        <v>0</v>
-      </c>
-      <c r="C15" s="2">
-        <v>0</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>9.9999999999999998E-13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1E-25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>26</v>
+      <c r="B18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2321,11 +2890,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025FDC18-195D-4905-B685-5FA04D5B62BC}">
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12423AB5-F589-4113-94B0-34077D332A14}">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.25" style="2" customWidth="1"/>
+    <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
     <col min="2" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -2334,7 +2903,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -2344,94 +2913,182 @@
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="D2" s="5"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="B3" s="2">
-        <v>0.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D3" s="5"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" s="2" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="3">
-        <v>1E-25</v>
-      </c>
-      <c r="C11" s="2">
-        <v>0</v>
+      <c r="D11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="2">
-        <v>0</v>
-      </c>
-      <c r="C12" s="3">
-        <v>1E-25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="D13" s="3"/>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="E14" s="3"/>
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F15" s="3"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1E-25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>26</v>
+      <c r="B18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/MetaData.xlsx
+++ b/MetaData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinzh\Dropbox\On_Going_Things\MultiScale_Project\PFM_Repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA74C404-F70F-497E-836E-F199DB7990CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF36071F-FF25-4AEB-A032-9FA0FF659D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -244,10 +244,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>bicgstab_ilu</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Linear solver max iteration</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -320,10 +316,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>LE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>LE solver (LE or GP)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -375,6 +367,14 @@
   </si>
   <si>
     <t>Orthopyroxene</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>direct</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GP</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -744,7 +744,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -782,12 +782,12 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B7" s="3">
         <v>1000000000</v>
@@ -795,7 +795,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B8" s="3">
         <v>9.9999999999999995E-7</v>
@@ -803,7 +803,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B9" s="2">
         <v>1</v>
@@ -814,7 +814,7 @@
         <v>29</v>
       </c>
       <c r="B10" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -827,7 +827,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -843,7 +843,7 @@
         <v>32</v>
       </c>
       <c r="B15" s="3">
-        <v>60000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -859,7 +859,7 @@
         <v>34</v>
       </c>
       <c r="B17" s="2">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -867,7 +867,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="2">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -931,7 +931,7 @@
         <v>43</v>
       </c>
       <c r="B26" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -987,7 +987,7 @@
         <v>50</v>
       </c>
       <c r="B33" s="2">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -995,12 +995,12 @@
         <v>51</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B35" s="3">
         <v>1E-10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B36" s="2">
         <v>500</v>
@@ -1016,7 +1016,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B37" s="2">
         <v>1</v>
@@ -1024,7 +1024,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B38" s="2">
         <v>2</v>
@@ -1032,7 +1032,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B39" s="2">
         <v>1</v>
@@ -1040,7 +1040,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B40" s="2">
         <v>1</v>
@@ -1048,7 +1048,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B41" s="2">
         <v>1</v>
@@ -1056,7 +1056,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B42" s="2">
         <v>2</v>
@@ -1064,7 +1064,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B43" s="2">
         <v>2</v>
@@ -1072,7 +1072,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B44" s="2">
         <v>1</v>
@@ -1080,12 +1080,12 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B47" s="2">
         <v>1</v>
@@ -1093,50 +1093,50 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B48" s="3">
-        <v>1.0000000000000001E-9</v>
+        <v>9.9999999999999998E-13</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B49" s="3">
-        <v>0.01</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B50" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B51" s="2">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B53" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1173,7 +1173,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -1218,7 +1218,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -1367,7 +1367,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -1381,7 +1381,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -1426,7 +1426,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -1606,7 +1606,7 @@
         <v>400</v>
       </c>
       <c r="C5" s="1">
-        <v>500000000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1617,7 +1617,7 @@
         <v>973</v>
       </c>
       <c r="C6" s="1">
-        <v>5000000000</v>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1666,7 +1666,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -1678,7 +1678,7 @@
         <v>19</v>
       </c>
       <c r="B4" s="2">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -1711,7 +1711,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -1734,7 +1734,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="3">
-        <v>9.9999999999999997E-29</v>
+        <v>1E-25</v>
       </c>
       <c r="C12" s="2">
         <v>0</v>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="3">
-        <v>9.9999999999999997E-29</v>
+        <v>1E-25</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="3">
-        <v>9.9999999999999997E-29</v>
+        <v>1E-25</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
@@ -1803,7 +1803,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>9.9999999999999997E-29</v>
+        <v>1E-25</v>
       </c>
       <c r="F15" s="2">
         <v>0</v>
@@ -1826,7 +1826,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>9.9999999999999997E-29</v>
+        <v>1E-25</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -1877,7 +1877,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -1889,7 +1889,7 @@
         <v>19</v>
       </c>
       <c r="B4" s="2">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -1922,7 +1922,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -2071,7 +2071,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -2085,7 +2085,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         <v>19</v>
       </c>
       <c r="B4" s="2">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -2130,7 +2130,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -2279,7 +2279,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -2293,7 +2293,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -2305,7 +2305,7 @@
         <v>19</v>
       </c>
       <c r="B4" s="2">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -2338,7 +2338,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -2487,7 +2487,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -2501,7 +2501,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -2513,7 +2513,7 @@
         <v>19</v>
       </c>
       <c r="B4" s="2">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -2546,7 +2546,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -2695,7 +2695,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -2709,7 +2709,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -2721,7 +2721,7 @@
         <v>19</v>
       </c>
       <c r="B4" s="2">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -2754,7 +2754,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -2903,7 +2903,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -2917,7 +2917,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -2929,7 +2929,7 @@
         <v>19</v>
       </c>
       <c r="B4" s="2">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -2962,7 +2962,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>

--- a/MetaData.xlsx
+++ b/MetaData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinzh\Dropbox\On_Going_Things\MultiScale_Project\PFM_Repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF36071F-FF25-4AEB-A032-9FA0FF659D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{022F9710-1780-4C8C-A268-AC1321364F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,6 +26,7 @@
     <sheet name="Melt(H18)" sheetId="10" r:id="rId11"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -316,6 +317,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>LE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>LE solver (LE or GP)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -371,10 +376,6 @@
   </si>
   <si>
     <t>direct</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GP</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -744,7 +745,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -787,7 +788,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" s="3">
         <v>1000000000</v>
@@ -795,7 +796,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B8" s="3">
         <v>9.9999999999999995E-7</v>
@@ -803,7 +804,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B9" s="2">
         <v>1</v>
@@ -814,7 +815,7 @@
         <v>29</v>
       </c>
       <c r="B10" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -822,7 +823,7 @@
         <v>30</v>
       </c>
       <c r="B11" s="3">
-        <v>0</v>
+        <v>5.0000000000000001E-4</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -835,7 +836,7 @@
         <v>31</v>
       </c>
       <c r="B14" s="3">
-        <v>10</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -843,7 +844,7 @@
         <v>32</v>
       </c>
       <c r="B15" s="3">
-        <v>1000000</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -859,7 +860,7 @@
         <v>34</v>
       </c>
       <c r="B17" s="2">
-        <v>0.02</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -867,7 +868,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="2">
-        <v>0.02</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -931,7 +932,7 @@
         <v>43</v>
       </c>
       <c r="B26" s="2">
-        <v>8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -963,7 +964,7 @@
         <v>47</v>
       </c>
       <c r="B30" s="2">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
@@ -987,7 +988,7 @@
         <v>50</v>
       </c>
       <c r="B33" s="2">
-        <v>24</v>
+        <v>250</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -995,7 +996,7 @@
         <v>51</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -1027,7 +1028,7 @@
         <v>55</v>
       </c>
       <c r="B38" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
@@ -1059,7 +1060,7 @@
         <v>59</v>
       </c>
       <c r="B42" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
@@ -1067,7 +1068,7 @@
         <v>60</v>
       </c>
       <c r="B43" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
@@ -1104,7 +1105,7 @@
         <v>67</v>
       </c>
       <c r="B49" s="3">
-        <v>10</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
@@ -1120,23 +1121,23 @@
         <v>69</v>
       </c>
       <c r="B51" s="2">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B53" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1173,7 +1174,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -1218,7 +1219,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -1367,7 +1368,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -1381,7 +1382,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -1426,7 +1427,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -1563,7 +1564,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.5" customWidth="1"/>
@@ -1592,7 +1593,7 @@
         <v>300000000</v>
       </c>
       <c r="B4">
-        <v>400</v>
+        <v>673</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1603,33 +1604,36 @@
         <v>300000000</v>
       </c>
       <c r="B5">
-        <v>400</v>
+        <v>673</v>
       </c>
       <c r="C5" s="1">
-        <v>100000000</v>
+        <v>1000000000</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>1000000000</v>
+        <v>300000000</v>
       </c>
       <c r="B6">
-        <v>973</v>
+        <v>673</v>
       </c>
       <c r="C6" s="1">
-        <v>1000000000</v>
+        <v>20000000000</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>1000000000</v>
+        <v>300000000</v>
       </c>
       <c r="B7">
-        <v>973</v>
+        <v>673</v>
       </c>
       <c r="C7" s="1">
-        <v>10000000000000</v>
-      </c>
+        <v>1000000000000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1666,7 +1670,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -1678,7 +1682,7 @@
         <v>19</v>
       </c>
       <c r="B4" s="2">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -1711,7 +1715,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -1877,7 +1881,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -1889,7 +1893,7 @@
         <v>19</v>
       </c>
       <c r="B4" s="2">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -1922,7 +1926,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -2071,7 +2075,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -2085,7 +2089,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -2097,7 +2101,7 @@
         <v>19</v>
       </c>
       <c r="B4" s="2">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -2130,7 +2134,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -2279,7 +2283,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -2293,7 +2297,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -2305,7 +2309,7 @@
         <v>19</v>
       </c>
       <c r="B4" s="2">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -2338,7 +2342,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -2487,7 +2491,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -2501,7 +2505,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -2513,7 +2517,7 @@
         <v>19</v>
       </c>
       <c r="B4" s="2">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -2546,7 +2550,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -2695,7 +2699,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -2709,7 +2713,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -2721,7 +2725,7 @@
         <v>19</v>
       </c>
       <c r="B4" s="2">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -2754,7 +2758,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -2903,7 +2907,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -2917,7 +2921,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -2962,7 +2966,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>

--- a/MetaData.xlsx
+++ b/MetaData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinzh\Dropbox\On_Going_Things\MultiScale_Project\PFM_Repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{022F9710-1780-4C8C-A268-AC1321364F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E32B0DC7-8B74-4500-8983-428C84AF9BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,6 @@
     <sheet name="Melt(H18)" sheetId="10" r:id="rId11"/>
   </sheets>
   <calcPr calcId="162913"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="88">
   <si>
     <t>PTt path. Put control points here. Interpolatation will be done automatically</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -375,7 +374,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>direct</t>
+    <t>Interface ramp grid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Interface zero kappa grid</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bicgstab_ilu</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -735,7 +742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{189715F9-88C1-473E-8CE8-6457A6A764DF}">
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29" style="2" customWidth="1"/>
@@ -815,7 +822,7 @@
         <v>29</v>
       </c>
       <c r="B10" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -823,7 +830,7 @@
         <v>30</v>
       </c>
       <c r="B11" s="3">
-        <v>5.0000000000000001E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -836,7 +843,7 @@
         <v>31</v>
       </c>
       <c r="B14" s="3">
-        <v>200</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -860,7 +867,7 @@
         <v>34</v>
       </c>
       <c r="B17" s="2">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -868,7 +875,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="2">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -932,7 +939,7 @@
         <v>43</v>
       </c>
       <c r="B26" s="2">
-        <v>50</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -964,7 +971,7 @@
         <v>47</v>
       </c>
       <c r="B30" s="2">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
@@ -996,7 +1003,7 @@
         <v>51</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -1097,7 +1104,7 @@
         <v>66</v>
       </c>
       <c r="B48" s="3">
-        <v>9.9999999999999998E-13</v>
+        <v>1.0000000000000001E-15</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
@@ -1105,7 +1112,7 @@
         <v>67</v>
       </c>
       <c r="B49" s="3">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
@@ -1121,7 +1128,7 @@
         <v>69</v>
       </c>
       <c r="B51" s="2">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
@@ -1137,7 +1144,23 @@
         <v>79</v>
       </c>
       <c r="B53" s="2">
-        <v>10</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B54" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B55" s="2">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2508,7 +2531,7 @@
         <v>80</v>
       </c>
       <c r="B3" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D3" s="5"/>
     </row>

--- a/MetaData.xlsx
+++ b/MetaData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinzh\Dropbox\On_Going_Things\MultiScale_Project\PFM_Repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E32B0DC7-8B74-4500-8983-428C84AF9BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186EB3D7-EE31-4805-AF29-D2F94E40E1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -822,7 +822,7 @@
         <v>29</v>
       </c>
       <c r="B10" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -843,7 +843,7 @@
         <v>31</v>
       </c>
       <c r="B14" s="3">
-        <v>10</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -851,7 +851,7 @@
         <v>32</v>
       </c>
       <c r="B15" s="3">
-        <v>5000000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -867,7 +867,7 @@
         <v>34</v>
       </c>
       <c r="B17" s="2">
-        <v>0.02</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -875,7 +875,7 @@
         <v>35</v>
       </c>
       <c r="B18" s="2">
-        <v>0.02</v>
+        <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
@@ -939,7 +939,7 @@
         <v>43</v>
       </c>
       <c r="B26" s="2">
-        <v>200</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -995,7 +995,7 @@
         <v>50</v>
       </c>
       <c r="B33" s="2">
-        <v>250</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -1144,7 +1144,7 @@
         <v>79</v>
       </c>
       <c r="B53" s="2">
-        <v>100</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
@@ -1616,7 +1616,7 @@
         <v>300000000</v>
       </c>
       <c r="B4">
-        <v>673</v>
+        <v>573</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1627,29 +1627,29 @@
         <v>300000000</v>
       </c>
       <c r="B5">
-        <v>673</v>
+        <v>573</v>
       </c>
       <c r="C5" s="1">
-        <v>1000000000</v>
+        <v>3000000000</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>300000000</v>
+        <v>1000000000</v>
       </c>
       <c r="B6">
-        <v>673</v>
+        <v>1073</v>
       </c>
       <c r="C6" s="1">
-        <v>20000000000</v>
+        <v>30000000000</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>300000000</v>
+        <v>1000000000</v>
       </c>
       <c r="B7">
-        <v>673</v>
+        <v>1073</v>
       </c>
       <c r="C7" s="1">
         <v>1000000000000000</v>
@@ -1761,7 +1761,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="3">
-        <v>1E-25</v>
+        <v>9.9999999999999997E-29</v>
       </c>
       <c r="C12" s="2">
         <v>0</v>
@@ -1784,7 +1784,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="3">
-        <v>1E-25</v>
+        <v>9.9999999999999997E-29</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="3">
-        <v>1E-25</v>
+        <v>9.9999999999999997E-29</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>1E-25</v>
+        <v>9.9999999999999997E-29</v>
       </c>
       <c r="F15" s="2">
         <v>0</v>
@@ -1853,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>1E-25</v>
+        <v>9.9999999999999997E-29</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">

--- a/MetaData.xlsx
+++ b/MetaData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinzh\Dropbox\On_Going_Things\MultiScale_Project\PFM_Repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186EB3D7-EE31-4805-AF29-D2F94E40E1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2735DCE-935A-413A-B396-E0E30377E0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,26 +16,41 @@
     <sheet name="Main" sheetId="4" r:id="rId1"/>
     <sheet name="PTt_Path" sheetId="1" r:id="rId2"/>
     <sheet name="Garnet" sheetId="2" r:id="rId3"/>
-    <sheet name="Olivine" sheetId="3" r:id="rId4"/>
-    <sheet name="Quartz" sheetId="6" r:id="rId5"/>
-    <sheet name="Kyanite" sheetId="7" r:id="rId6"/>
-    <sheet name="Clinopyroxene" sheetId="8" r:id="rId7"/>
-    <sheet name="Orthopyroxene" sheetId="11" r:id="rId8"/>
-    <sheet name="Feldspar" sheetId="9" r:id="rId9"/>
-    <sheet name="Melt" sheetId="5" r:id="rId10"/>
-    <sheet name="Melt(H18)" sheetId="10" r:id="rId11"/>
+    <sheet name="Staurolite" sheetId="12" r:id="rId4"/>
+    <sheet name="Olivine" sheetId="3" r:id="rId5"/>
+    <sheet name="Quartz" sheetId="6" r:id="rId6"/>
+    <sheet name="Kyanite" sheetId="7" r:id="rId7"/>
+    <sheet name="Clinopyroxene" sheetId="8" r:id="rId8"/>
+    <sheet name="Orthopyroxene" sheetId="11" r:id="rId9"/>
+    <sheet name="Brucite" sheetId="13" r:id="rId10"/>
+    <sheet name="Periclase" sheetId="14" r:id="rId11"/>
+    <sheet name="Fluid-H2O" sheetId="15" r:id="rId12"/>
+    <sheet name="Feldspar" sheetId="9" r:id="rId13"/>
+    <sheet name="Melt" sheetId="5" r:id="rId14"/>
+    <sheet name="Melt(H18)" sheetId="10" r:id="rId15"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="94">
   <si>
     <t>PTt path. Put control points here. Interpolatation will be done automatically</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -145,9 +160,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>solution_models_PFM</t>
-  </si>
-  <si>
     <t>Molar volume</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -383,6 +395,34 @@
   </si>
   <si>
     <t>bicgstab_ilu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Staurolite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>metapelite_PFM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brucite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Periclase</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fluid-H2O</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -742,7 +782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{189715F9-88C1-473E-8CE8-6457A6A764DF}">
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29" style="2" customWidth="1"/>
@@ -750,12 +790,12 @@
     <col min="3" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
@@ -766,97 +806,94 @@
         <v>15</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="B4" s="3">
         <v>2.0000000000000002E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B7" s="3">
         <v>1000000000</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B8" s="3">
         <v>9.9999999999999995E-7</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B9" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
+      <c r="B11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>31</v>
       </c>
       <c r="B14" s="3">
         <v>100000</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B15" s="3">
         <v>100000000</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B16" s="3">
         <v>9.9999999999999998E-13</v>
@@ -864,7 +901,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B17" s="2">
         <v>2.5000000000000001E-2</v>
@@ -872,7 +909,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B18" s="2">
         <v>2.5000000000000001E-2</v>
@@ -880,7 +917,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B19" s="2">
         <v>100</v>
@@ -888,7 +925,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B20" s="2">
         <v>0</v>
@@ -896,7 +933,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B21" s="2">
         <v>8</v>
@@ -904,7 +941,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B22" s="2">
         <v>1.1499999999999999</v>
@@ -912,7 +949,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B23" s="2">
         <v>0.5</v>
@@ -920,7 +957,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B24" s="2">
         <v>0.25</v>
@@ -928,7 +965,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B25" s="3">
         <v>1E-8</v>
@@ -936,7 +973,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B26" s="2">
         <v>3</v>
@@ -944,7 +981,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B27" s="2">
         <v>1</v>
@@ -952,7 +989,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B28" s="2">
         <v>0</v>
@@ -960,7 +997,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B29" s="2">
         <v>1</v>
@@ -968,15 +1005,15 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B30" s="2">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B31" s="2">
         <v>0</v>
@@ -984,7 +1021,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B32" s="3">
         <v>1E-8</v>
@@ -992,23 +1029,23 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B33" s="2">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B35" s="3">
         <v>1E-10</v>
@@ -1016,7 +1053,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B36" s="2">
         <v>500</v>
@@ -1024,7 +1061,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B37" s="2">
         <v>1</v>
@@ -1032,7 +1069,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B38" s="2">
         <v>5</v>
@@ -1040,7 +1077,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B39" s="2">
         <v>1</v>
@@ -1048,7 +1085,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B40" s="2">
         <v>1</v>
@@ -1056,7 +1093,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B41" s="2">
         <v>1</v>
@@ -1064,7 +1101,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B42" s="2">
         <v>5</v>
@@ -1072,7 +1109,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B43" s="2">
         <v>5</v>
@@ -1080,7 +1117,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B44" s="2">
         <v>1</v>
@@ -1088,12 +1125,12 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B47" s="2">
         <v>1</v>
@@ -1101,7 +1138,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B48" s="3">
         <v>1.0000000000000001E-15</v>
@@ -1109,15 +1146,15 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B49" s="3">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B50" s="2">
         <v>0</v>
@@ -1125,7 +1162,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B51" s="2">
         <v>0.2</v>
@@ -1133,15 +1170,15 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B53" s="2">
         <v>10</v>
@@ -1149,7 +1186,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B54" s="2">
         <v>2</v>
@@ -1157,10 +1194,10 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B55" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1170,6 +1207,976 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B978AE48-7807-407B-9571-6A3F534D5BAF}">
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1E-26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A946726-7D80-4B62-BBCE-48A4E6603B25}">
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1E-26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{802959B0-0E72-42B5-BB24-FADA17AFE75F}">
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1E-26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12423AB5-F589-4113-94B0-34077D332A14}">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1E-25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025FDC18-195D-4905-B685-5FA04D5B62BC}">
   <dimension ref="A1:F18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -1197,7 +2204,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -1242,7 +2249,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -1377,7 +2384,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41D8EF3E-EA7F-4736-966B-1CF8D5A8AF27}">
   <dimension ref="A1:F18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -1391,7 +2398,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -1405,7 +2412,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -1450,7 +2457,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -1616,7 +2623,7 @@
         <v>300000000</v>
       </c>
       <c r="B4">
-        <v>573</v>
+        <v>1000</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1627,18 +2634,18 @@
         <v>300000000</v>
       </c>
       <c r="B5">
-        <v>573</v>
+        <v>1000</v>
       </c>
       <c r="C5" s="1">
-        <v>3000000000</v>
+        <v>10000000000</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>1000000000</v>
+        <v>300000000</v>
       </c>
       <c r="B6">
-        <v>1073</v>
+        <v>1000</v>
       </c>
       <c r="C6" s="1">
         <v>30000000000</v>
@@ -1646,10 +2653,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>1000000000</v>
+        <v>300000000</v>
       </c>
       <c r="B7">
-        <v>1073</v>
+        <v>1000</v>
       </c>
       <c r="C7" s="1">
         <v>1000000000000000</v>
@@ -1667,14 +2674,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E05623AC-7B59-47E4-814D-E3135FA16D14}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
     <col min="2" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
@@ -1682,7 +2689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -1691,16 +2698,16 @@
       </c>
       <c r="D2" s="5"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
       </c>
       <c r="D3" s="5"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>19</v>
       </c>
@@ -1708,7 +2715,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
@@ -1716,29 +2723,29 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -1753,15 +2760,18 @@
         <v>17</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="3">
-        <v>9.9999999999999997E-29</v>
+        <v>1E-26</v>
       </c>
       <c r="C12" s="2">
         <v>0</v>
@@ -1775,8 +2785,11 @@
       <c r="F12" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
@@ -1784,7 +2797,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="3">
-        <v>9.9999999999999997E-29</v>
+        <v>1E-26</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
@@ -1795,8 +2808,11 @@
       <c r="F13" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
@@ -1807,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="3">
-        <v>9.9999999999999997E-29</v>
+        <v>1E-26</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
@@ -1815,8 +2831,11 @@
       <c r="F14" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
@@ -1830,15 +2849,18 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>9.9999999999999997E-29</v>
+        <v>1E-26</v>
       </c>
       <c r="F15" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="B16" s="2">
         <v>0</v>
@@ -1853,20 +2875,48 @@
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>9.9999999999999997E-29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
+        <v>1E-26</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1E-26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B21" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1877,6 +2927,260 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B94BE2D7-D4A1-42CE-8DF9-A1185EC16DD5}">
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1E-26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AD31C97-603F-4CE3-9593-050F54A5E117}">
   <dimension ref="A1:F18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -1904,7 +3208,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
@@ -1949,215 +3253,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="3">
-        <v>1E-25</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="2">
-        <v>0</v>
-      </c>
-      <c r="C13" s="3">
-        <v>1E-25</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="2">
-        <v>0</v>
-      </c>
-      <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="3">
-        <v>1E-25</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="2">
-        <v>0</v>
-      </c>
-      <c r="C15" s="2">
-        <v>0</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1E-25</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="2">
-        <v>0</v>
-      </c>
-      <c r="C16" s="2">
-        <v>0</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3">
-        <v>1E-25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FF107C2-8A37-4D64-A550-09EEF500952A}">
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="5"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B3" s="2">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -2293,23 +3389,23 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63151BAD-3F80-45D4-892B-9A6DD90D0F1A}">
-  <dimension ref="A1:F18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FF107C2-8A37-4D64-A550-09EEF500952A}">
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
     <col min="2" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -2318,16 +3414,16 @@
       </c>
       <c r="D2" s="5"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
       </c>
       <c r="D3" s="5"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>19</v>
       </c>
@@ -2335,7 +3431,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
@@ -2343,29 +3439,29 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -2380,15 +3476,18 @@
         <v>17</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="3">
-        <v>1E-25</v>
+        <v>1E-26</v>
       </c>
       <c r="C12" s="2">
         <v>0</v>
@@ -2402,8 +3501,11 @@
       <c r="F12" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
@@ -2411,7 +3513,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="3">
-        <v>1E-25</v>
+        <v>1E-26</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
@@ -2422,8 +3524,11 @@
       <c r="F13" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
@@ -2434,7 +3539,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="3">
-        <v>1E-25</v>
+        <v>1E-26</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
@@ -2442,8 +3547,11 @@
       <c r="F14" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
@@ -2457,15 +3565,18 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>1E-25</v>
+        <v>1E-26</v>
       </c>
       <c r="F15" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="B16" s="2">
         <v>0</v>
@@ -2480,17 +3591,48 @@
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>1E-25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
+        <v>1E-26</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1E-26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B21" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2501,23 +3643,23 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1655C2AE-3514-4AA5-8179-DD282EB7D835}">
-  <dimension ref="A1:F18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63151BAD-3F80-45D4-892B-9A6DD90D0F1A}">
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
     <col min="2" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -2526,16 +3668,16 @@
       </c>
       <c r="D2" s="5"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B3" s="2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D3" s="5"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>19</v>
       </c>
@@ -2543,7 +3685,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
@@ -2551,29 +3693,29 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -2588,15 +3730,18 @@
         <v>17</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="3">
-        <v>1E-25</v>
+        <v>1E-26</v>
       </c>
       <c r="C12" s="2">
         <v>0</v>
@@ -2610,8 +3755,11 @@
       <c r="F12" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
@@ -2619,7 +3767,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="3">
-        <v>1E-25</v>
+        <v>1E-26</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
@@ -2630,8 +3778,11 @@
       <c r="F13" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
@@ -2642,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="3">
-        <v>1E-25</v>
+        <v>1E-26</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
@@ -2650,8 +3801,11 @@
       <c r="F14" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
@@ -2665,15 +3819,18 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>1E-25</v>
+        <v>1E-26</v>
       </c>
       <c r="F15" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="B16" s="2">
         <v>0</v>
@@ -2688,17 +3845,48 @@
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>1E-25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
+        <v>1E-26</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1E-26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B21" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2709,23 +3897,23 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6592A610-98F2-4892-B0FE-DFC4003883EF}">
-  <dimension ref="A1:F18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1655C2AE-3514-4AA5-8179-DD282EB7D835}">
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
     <col min="2" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -2734,16 +3922,16 @@
       </c>
       <c r="D2" s="5"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B3" s="2">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="D3" s="5"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>19</v>
       </c>
@@ -2751,7 +3939,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
@@ -2759,29 +3947,29 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -2796,15 +3984,18 @@
         <v>17</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="3">
-        <v>1E-25</v>
+        <v>1E-26</v>
       </c>
       <c r="C12" s="2">
         <v>0</v>
@@ -2818,8 +4009,11 @@
       <c r="F12" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
@@ -2827,7 +4021,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="3">
-        <v>1E-25</v>
+        <v>1E-26</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
@@ -2838,8 +4032,11 @@
       <c r="F13" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
@@ -2850,7 +4047,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="3">
-        <v>1E-25</v>
+        <v>1E-26</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
@@ -2858,8 +4055,11 @@
       <c r="F14" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
@@ -2873,15 +4073,18 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>1E-25</v>
+        <v>1E-26</v>
       </c>
       <c r="F15" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="B16" s="2">
         <v>0</v>
@@ -2896,17 +4099,48 @@
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>1E-25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
+        <v>1E-26</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1E-26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B21" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2917,23 +4151,23 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12423AB5-F589-4113-94B0-34077D332A14}">
-  <dimension ref="A1:F18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6592A610-98F2-4892-B0FE-DFC4003883EF}">
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
     <col min="2" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -2942,24 +4176,24 @@
       </c>
       <c r="D2" s="5"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
       </c>
       <c r="D3" s="5"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
@@ -2967,29 +4201,29 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>14</v>
@@ -3004,15 +4238,18 @@
         <v>17</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="3">
-        <v>1E-25</v>
+        <v>1E-26</v>
       </c>
       <c r="C12" s="2">
         <v>0</v>
@@ -3026,8 +4263,11 @@
       <c r="F12" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
@@ -3035,7 +4275,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="3">
-        <v>1E-25</v>
+        <v>1E-26</v>
       </c>
       <c r="D13" s="2">
         <v>0</v>
@@ -3046,8 +4286,11 @@
       <c r="F13" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
@@ -3058,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="3">
-        <v>1E-25</v>
+        <v>1E-26</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
@@ -3066,8 +4309,11 @@
       <c r="F14" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
@@ -3081,15 +4327,18 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>1E-25</v>
+        <v>1E-26</v>
       </c>
       <c r="F15" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="B16" s="2">
         <v>0</v>
@@ -3104,17 +4353,48 @@
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>1E-25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
+        <v>1E-26</v>
+      </c>
+      <c r="G16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1E-26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B21" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>23</v>
       </c>
     </row>

--- a/MetaData.xlsx
+++ b/MetaData.xlsx
@@ -8,26 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xinzh\Dropbox\On_Going_Things\MultiScale_Project\PFM_Repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2735DCE-935A-413A-B396-E0E30377E0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A74FD0B9-3BF1-4795-A2AE-369E9CC62AB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="4" r:id="rId1"/>
     <sheet name="PTt_Path" sheetId="1" r:id="rId2"/>
-    <sheet name="Garnet" sheetId="2" r:id="rId3"/>
-    <sheet name="Staurolite" sheetId="12" r:id="rId4"/>
-    <sheet name="Olivine" sheetId="3" r:id="rId5"/>
-    <sheet name="Quartz" sheetId="6" r:id="rId6"/>
-    <sheet name="Kyanite" sheetId="7" r:id="rId7"/>
-    <sheet name="Clinopyroxene" sheetId="8" r:id="rId8"/>
-    <sheet name="Orthopyroxene" sheetId="11" r:id="rId9"/>
-    <sheet name="Brucite" sheetId="13" r:id="rId10"/>
-    <sheet name="Periclase" sheetId="14" r:id="rId11"/>
-    <sheet name="Fluid-H2O" sheetId="15" r:id="rId12"/>
-    <sheet name="Feldspar" sheetId="9" r:id="rId13"/>
-    <sheet name="Melt" sheetId="5" r:id="rId14"/>
-    <sheet name="Melt(H18)" sheetId="10" r:id="rId15"/>
+    <sheet name="Interface" sheetId="16" r:id="rId3"/>
+    <sheet name="Garnet" sheetId="2" r:id="rId4"/>
+    <sheet name="Staurolite" sheetId="12" r:id="rId5"/>
+    <sheet name="Olivine" sheetId="3" r:id="rId6"/>
+    <sheet name="Quartz" sheetId="6" r:id="rId7"/>
+    <sheet name="Kyanite" sheetId="7" r:id="rId8"/>
+    <sheet name="Clinopyroxene" sheetId="8" r:id="rId9"/>
+    <sheet name="Orthopyroxene" sheetId="11" r:id="rId10"/>
+    <sheet name="Brucite" sheetId="13" r:id="rId11"/>
+    <sheet name="Periclase" sheetId="14" r:id="rId12"/>
+    <sheet name="Fluid-H2O" sheetId="15" r:id="rId13"/>
+    <sheet name="Feldspar" sheetId="9" r:id="rId14"/>
+    <sheet name="Melt" sheetId="5" r:id="rId15"/>
+    <sheet name="Melt(H18)" sheetId="10" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="95">
   <si>
     <t>PTt path. Put control points here. Interpolatation will be done automatically</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -420,6 +421,9 @@
   <si>
     <t>Periclase</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fluid-H2O</t>
   </si>
   <si>
     <t>Fluid-H2O</t>
@@ -976,7 +980,7 @@
         <v>42</v>
       </c>
       <c r="B26" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
@@ -1032,7 +1036,7 @@
         <v>49</v>
       </c>
       <c r="B33" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
@@ -1207,8 +1211,8 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B978AE48-7807-407B-9571-6A3F534D5BAF}">
-  <dimension ref="A1:G21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6592A610-98F2-4892-B0FE-DFC4003883EF}">
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
@@ -1220,7 +1224,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -1243,72 +1247,87 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.4</v>
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>88</v>
+      <c r="B11" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1E-26</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -1325,16 +1344,16 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2">
         <v>0</v>
       </c>
-      <c r="C13" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1E-26</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
@@ -1348,7 +1367,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" s="2">
         <v>0</v>
@@ -1356,11 +1375,11 @@
       <c r="C14" s="2">
         <v>0</v>
       </c>
-      <c r="D14" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1E-26</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -1371,7 +1390,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="B15" s="2">
         <v>0</v>
@@ -1382,11 +1401,11 @@
       <c r="D15" s="2">
         <v>0</v>
       </c>
-      <c r="E15" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1E-26</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
@@ -1394,7 +1413,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B16" s="2">
         <v>0</v>
@@ -1409,48 +1428,25 @@
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" s="2">
-        <v>0</v>
-      </c>
-      <c r="C17" s="2">
-        <v>0</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1E-26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1E-26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B20" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1461,8 +1457,8 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A946726-7D80-4B62-BBCE-48A4E6603B25}">
-  <dimension ref="A1:G21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B978AE48-7807-407B-9571-6A3F534D5BAF}">
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
@@ -1474,7 +1470,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -1497,72 +1493,87 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.4</v>
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>88</v>
+      <c r="B11" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1E-26</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -1579,16 +1590,16 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2">
         <v>0</v>
       </c>
-      <c r="C13" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1E-26</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
@@ -1602,7 +1613,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" s="2">
         <v>0</v>
@@ -1610,11 +1621,11 @@
       <c r="C14" s="2">
         <v>0</v>
       </c>
-      <c r="D14" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1E-26</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -1625,7 +1636,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="B15" s="2">
         <v>0</v>
@@ -1636,11 +1647,11 @@
       <c r="D15" s="2">
         <v>0</v>
       </c>
-      <c r="E15" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1E-26</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
@@ -1648,7 +1659,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B16" s="2">
         <v>0</v>
@@ -1663,48 +1674,25 @@
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" s="2">
-        <v>0</v>
-      </c>
-      <c r="C17" s="2">
-        <v>0</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1E-26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1E-26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B20" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1715,8 +1703,8 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{802959B0-0E72-42B5-BB24-FADA17AFE75F}">
-  <dimension ref="A1:G21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A946726-7D80-4B62-BBCE-48A4E6603B25}">
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
@@ -1728,7 +1716,7 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -1751,72 +1739,87 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.1</v>
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>88</v>
+      <c r="B11" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1E-26</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -1833,16 +1836,16 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2">
         <v>0</v>
       </c>
-      <c r="C13" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1E-26</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
@@ -1856,7 +1859,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" s="2">
         <v>0</v>
@@ -1864,11 +1867,11 @@
       <c r="C14" s="2">
         <v>0</v>
       </c>
-      <c r="D14" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1E-26</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -1879,7 +1882,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="B15" s="2">
         <v>0</v>
@@ -1890,11 +1893,11 @@
       <c r="D15" s="2">
         <v>0</v>
       </c>
-      <c r="E15" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1E-26</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
@@ -1902,7 +1905,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B16" s="2">
         <v>0</v>
@@ -1917,48 +1920,25 @@
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" s="2">
-        <v>0</v>
-      </c>
-      <c r="C17" s="2">
-        <v>0</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1E-26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1E-26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B20" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1969,8 +1949,254 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{802959B0-0E72-42B5-BB24-FADA17AFE75F}">
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1E-26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12423AB5-F589-4113-94B0-34077D332A14}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
@@ -2005,69 +2231,81 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.5</v>
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>18</v>
+      <c r="B11" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="3">
+        <v>15</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3">
         <v>1E-25</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -2081,16 +2319,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2">
         <v>0</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
         <v>1E-25</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
@@ -2101,7 +2339,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" s="2">
         <v>0</v>
@@ -2109,11 +2347,11 @@
       <c r="C14" s="2">
         <v>0</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>1E-25</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -2121,7 +2359,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" s="2">
         <v>0</v>
@@ -2132,41 +2370,21 @@
       <c r="D15" s="2">
         <v>0</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <v>1E-25</v>
       </c>
-      <c r="F15" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="2">
-        <v>0</v>
-      </c>
-      <c r="C16" s="2">
-        <v>0</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3">
-        <v>1E-25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B17" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2176,9 +2394,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025FDC18-195D-4905-B685-5FA04D5B62BC}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
@@ -2213,69 +2431,81 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.5</v>
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>18</v>
+      <c r="B11" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="3">
+        <v>15</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3">
         <v>1E-25</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -2289,16 +2519,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2">
         <v>0</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
         <v>1E-25</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
@@ -2309,7 +2539,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" s="2">
         <v>0</v>
@@ -2317,11 +2547,11 @@
       <c r="C14" s="2">
         <v>0</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>1E-25</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -2329,7 +2559,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" s="2">
         <v>0</v>
@@ -2340,41 +2570,21 @@
       <c r="D15" s="2">
         <v>0</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <v>1E-25</v>
       </c>
-      <c r="F15" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="2">
-        <v>0</v>
-      </c>
-      <c r="C16" s="2">
-        <v>0</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3">
-        <v>1E-25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B17" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2384,9 +2594,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41D8EF3E-EA7F-4736-966B-1CF8D5A8AF27}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
@@ -2421,69 +2631,81 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.5</v>
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>18</v>
+      <c r="B11" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="3">
+        <v>15</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3">
         <v>1E-25</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -2497,16 +2719,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2">
         <v>0</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
         <v>1E-25</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
@@ -2517,7 +2739,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" s="2">
         <v>0</v>
@@ -2525,11 +2747,11 @@
       <c r="C14" s="2">
         <v>0</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>1E-25</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -2537,7 +2759,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" s="2">
         <v>0</v>
@@ -2548,41 +2770,21 @@
       <c r="D15" s="2">
         <v>0</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <v>1E-25</v>
       </c>
-      <c r="F15" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="2">
-        <v>0</v>
-      </c>
-      <c r="C16" s="2">
-        <v>0</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3">
-        <v>1E-25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B17" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2673,8 +2875,106 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7AA72EF-856F-4552-8144-92AC8307D4B3}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3">
+        <v>0.8</v>
+      </c>
+      <c r="C3">
+        <v>0.8</v>
+      </c>
+      <c r="D3">
+        <v>0.8</v>
+      </c>
+      <c r="E3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4">
+        <v>0.8</v>
+      </c>
+      <c r="C4">
+        <v>0.8</v>
+      </c>
+      <c r="D4">
+        <v>0.8</v>
+      </c>
+      <c r="E4">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5">
+        <v>0.8</v>
+      </c>
+      <c r="C5">
+        <v>0.8</v>
+      </c>
+      <c r="D5">
+        <v>0.8</v>
+      </c>
+      <c r="E5">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6">
+        <v>0.1</v>
+      </c>
+      <c r="C6">
+        <v>0.1</v>
+      </c>
+      <c r="D6">
+        <v>0.1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1.0000000000000001E-5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E05623AC-7B59-47E4-814D-E3135FA16D14}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
@@ -2709,72 +3009,87 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.4</v>
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>88</v>
+      <c r="B11" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1E-26</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -2791,16 +3106,16 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2">
         <v>0</v>
       </c>
-      <c r="C13" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1E-26</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
@@ -2814,7 +3129,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" s="2">
         <v>0</v>
@@ -2822,11 +3137,11 @@
       <c r="C14" s="2">
         <v>0</v>
       </c>
-      <c r="D14" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1E-26</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -2837,7 +3152,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="B15" s="2">
         <v>0</v>
@@ -2848,11 +3163,11 @@
       <c r="D15" s="2">
         <v>0</v>
       </c>
-      <c r="E15" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1E-26</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
@@ -2860,7 +3175,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B16" s="2">
         <v>0</v>
@@ -2875,48 +3190,25 @@
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" s="2">
-        <v>0</v>
-      </c>
-      <c r="C17" s="2">
-        <v>0</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1E-26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1E-26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B20" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2926,9 +3218,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B94BE2D7-D4A1-42CE-8DF9-A1185EC16DD5}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
@@ -2963,72 +3255,87 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.4</v>
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>88</v>
+      <c r="B11" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1E-26</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -3045,16 +3352,16 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2">
         <v>0</v>
       </c>
-      <c r="C13" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1E-26</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
@@ -3068,7 +3375,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" s="2">
         <v>0</v>
@@ -3076,11 +3383,11 @@
       <c r="C14" s="2">
         <v>0</v>
       </c>
-      <c r="D14" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1E-26</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -3091,7 +3398,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="B15" s="2">
         <v>0</v>
@@ -3102,11 +3409,11 @@
       <c r="D15" s="2">
         <v>0</v>
       </c>
-      <c r="E15" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1E-26</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
@@ -3114,7 +3421,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B16" s="2">
         <v>0</v>
@@ -3129,48 +3436,25 @@
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" s="2">
-        <v>0</v>
-      </c>
-      <c r="C17" s="2">
-        <v>0</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1E-26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1E-26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B20" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3180,9 +3464,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AD31C97-603F-4CE3-9593-050F54A5E117}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
@@ -3217,69 +3501,81 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.4</v>
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>18</v>
+      <c r="B11" s="3">
+        <v>1E-25</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="3">
+        <v>15</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3">
         <v>1E-25</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -3293,16 +3589,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2">
         <v>0</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
         <v>1E-25</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
@@ -3313,7 +3609,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" s="2">
         <v>0</v>
@@ -3321,11 +3617,11 @@
       <c r="C14" s="2">
         <v>0</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>1E-25</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -3333,7 +3629,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B15" s="2">
         <v>0</v>
@@ -3344,41 +3640,21 @@
       <c r="D15" s="2">
         <v>0</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <v>1E-25</v>
       </c>
-      <c r="F15" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="2">
-        <v>0</v>
-      </c>
-      <c r="C16" s="2">
-        <v>0</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3">
-        <v>1E-25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B17" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3388,9 +3664,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FF107C2-8A37-4D64-A550-09EEF500952A}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
@@ -3425,72 +3701,87 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.4</v>
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>88</v>
+      <c r="B11" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1E-26</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -3507,16 +3798,16 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2">
         <v>0</v>
       </c>
-      <c r="C13" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1E-26</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
@@ -3530,7 +3821,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" s="2">
         <v>0</v>
@@ -3538,11 +3829,11 @@
       <c r="C14" s="2">
         <v>0</v>
       </c>
-      <c r="D14" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1E-26</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -3553,7 +3844,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="B15" s="2">
         <v>0</v>
@@ -3564,11 +3855,11 @@
       <c r="D15" s="2">
         <v>0</v>
       </c>
-      <c r="E15" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1E-26</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
@@ -3576,7 +3867,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B16" s="2">
         <v>0</v>
@@ -3591,48 +3882,25 @@
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" s="2">
-        <v>0</v>
-      </c>
-      <c r="C17" s="2">
-        <v>0</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1E-26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1E-26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B20" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3642,9 +3910,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63151BAD-3F80-45D4-892B-9A6DD90D0F1A}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
@@ -3679,72 +3947,87 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.4</v>
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>88</v>
+      <c r="B11" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1E-26</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -3761,16 +4044,16 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2">
         <v>0</v>
       </c>
-      <c r="C13" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1E-26</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
@@ -3784,7 +4067,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" s="2">
         <v>0</v>
@@ -3792,11 +4075,11 @@
       <c r="C14" s="2">
         <v>0</v>
       </c>
-      <c r="D14" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1E-26</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -3807,7 +4090,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="B15" s="2">
         <v>0</v>
@@ -3818,11 +4101,11 @@
       <c r="D15" s="2">
         <v>0</v>
       </c>
-      <c r="E15" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1E-26</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
@@ -3830,7 +4113,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B16" s="2">
         <v>0</v>
@@ -3845,48 +4128,25 @@
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" s="2">
-        <v>0</v>
-      </c>
-      <c r="C17" s="2">
-        <v>0</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1E-26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1E-26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B20" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3896,9 +4156,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1655C2AE-3514-4AA5-8179-DD282EB7D835}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
@@ -3933,72 +4193,87 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.4</v>
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
     </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>88</v>
+      <c r="B11" s="3">
+        <v>1E-26</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1E-26</v>
       </c>
       <c r="D12" s="2">
         <v>0</v>
@@ -4015,16 +4290,16 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2">
         <v>0</v>
       </c>
-      <c r="C13" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1E-26</v>
       </c>
       <c r="E13" s="2">
         <v>0</v>
@@ -4038,7 +4313,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B14" s="2">
         <v>0</v>
@@ -4046,11 +4321,11 @@
       <c r="C14" s="2">
         <v>0</v>
       </c>
-      <c r="D14" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1E-26</v>
       </c>
       <c r="F14" s="2">
         <v>0</v>
@@ -4061,7 +4336,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="B15" s="2">
         <v>0</v>
@@ -4072,11 +4347,11 @@
       <c r="D15" s="2">
         <v>0</v>
       </c>
-      <c r="E15" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1E-26</v>
       </c>
       <c r="G15" s="2">
         <v>0</v>
@@ -4084,7 +4359,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B16" s="2">
         <v>0</v>
@@ -4099,302 +4374,25 @@
         <v>0</v>
       </c>
       <c r="F16" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" s="2">
-        <v>0</v>
-      </c>
-      <c r="C17" s="2">
-        <v>0</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1E-26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1E-26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B20" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6592A610-98F2-4892-B0FE-DFC4003883EF}">
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="23.25" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="5"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B3" s="2">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" s="2">
-        <v>0</v>
-      </c>
-      <c r="C13" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
-      <c r="G13" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="2">
-        <v>0</v>
-      </c>
-      <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2">
-        <v>0</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="2">
-        <v>0</v>
-      </c>
-      <c r="C15" s="2">
-        <v>0</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B16" s="2">
-        <v>0</v>
-      </c>
-      <c r="C16" s="2">
-        <v>0</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3">
-        <v>1E-26</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" s="2">
-        <v>0</v>
-      </c>
-      <c r="C17" s="2">
-        <v>0</v>
-      </c>
-      <c r="D17" s="2">
-        <v>0</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1E-26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>23</v>
       </c>
     </row>
